--- a/writings/Paper_Screening.xlsx
+++ b/writings/Paper_Screening.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMP9800\github\gradproj\writings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEFD40F-424A-435C-9B24-608649F5B9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04D5781-1B5A-4FFB-AB0C-D4FCFA6C25F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1035" windowWidth="29040" windowHeight="15720" tabRatio="337" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="337" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="665">
   <si>
     <t>Title</t>
   </si>
@@ -2764,6 +2764,111 @@
   <si>
     <t xml:space="preserve">Accuracy
 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROUGE metric
+Human rating</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Precision at 1 (P@1)
+Mean Reciprocal Rank(MRR)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>F1
+MRR
+Recall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Precision
+Recall
+F1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy (YES/NO Questions)
+MRR (Factoid Questions)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recall @ K
+MRR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>quantitative performance against specialist models：
+ - FID
+ - MS-SSIM
+realism and text-alignment：
+ - Recall
+ - Precision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Accuracy
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FID
+Kernel Inception Distance (KID)
+F1, Balanced Accuracy, AUC (Classification Performance)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FID
+Generative Precision and Recall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BLUE， ROUGE (Language generation)
+FID (image)
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FID
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FID
+CLIP Score</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy (Classification)
+Precision @ {1,2,5,10} (Image-text retreival)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUC, F1, Accuracy (Classification)
+CheXpert@k Score
+FID (Image generation)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLEU
+Precision, Recall, F1
+ROUGE
+CIDEr
+METEROR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Human Evaluation
+FID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Classification evaluation metrics for a variety of datasets</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2881,7 +2986,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2925,8 +3030,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3245,7 +3359,7 @@
     <col min="9" max="9" width="7.88671875" style="1" customWidth="1"/>
     <col min="10" max="10" width="17.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="29.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.44140625" style="3" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="11.88671875" customWidth="1"/>
     <col min="15" max="15" width="8.77734375" customWidth="1"/>
@@ -3257,40 +3371,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="16" t="s">
         <v>636</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -3368,7 +3482,7 @@
         <v>4</v>
       </c>
       <c r="R2">
-        <f>SUM(M2:Q2)</f>
+        <f t="shared" ref="R2:R33" si="0">SUM(M2:Q2)</f>
         <v>22</v>
       </c>
       <c r="S2" t="s">
@@ -3431,7 +3545,7 @@
         <v>5</v>
       </c>
       <c r="R3">
-        <f>SUM(M3:Q3)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="S3" t="s">
@@ -3494,7 +3608,7 @@
         <v>5</v>
       </c>
       <c r="R4">
-        <f>SUM(M4:Q4)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="S4" t="s">
@@ -3554,7 +3668,7 @@
         <v>4</v>
       </c>
       <c r="R5">
-        <f>SUM(M5:Q5)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="S5" t="s">
@@ -3617,7 +3731,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <f>SUM(M6:Q6)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="S6" t="s">
@@ -3674,7 +3788,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <f>SUM(M7:Q7)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="S7" t="s">
@@ -3728,7 +3842,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <f>SUM(M8:Q8)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="S8" t="s">
@@ -3782,7 +3896,7 @@
         <v>5</v>
       </c>
       <c r="R9">
-        <f>SUM(M9:Q9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="S9" t="s">
@@ -3842,7 +3956,7 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <f>SUM(M10:Q10)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S10" t="s">
@@ -3896,7 +4010,7 @@
         <v>5</v>
       </c>
       <c r="R11">
-        <f>SUM(M11:Q11)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S11" t="s">
@@ -3950,7 +4064,7 @@
         <v>5</v>
       </c>
       <c r="R12">
-        <f>SUM(M12:Q12)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S12" t="s">
@@ -4007,7 +4121,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <f>SUM(M13:Q13)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S13" t="s">
@@ -4061,7 +4175,7 @@
         <v>5</v>
       </c>
       <c r="R14">
-        <f>SUM(M14:Q14)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S14" t="s">
@@ -4099,6 +4213,7 @@
       <c r="K15" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="L15" s="1"/>
       <c r="M15">
         <v>5</v>
       </c>
@@ -4115,7 +4230,7 @@
         <v>5</v>
       </c>
       <c r="R15">
-        <f>SUM(M15:Q15)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="T15" s="1" t="s">
@@ -4153,6 +4268,7 @@
       <c r="K16" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="L16" s="1"/>
       <c r="M16">
         <v>5</v>
       </c>
@@ -4169,7 +4285,7 @@
         <v>5</v>
       </c>
       <c r="R16">
-        <f>SUM(M16:Q16)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="T16" s="1" t="s">
@@ -4207,6 +4323,7 @@
       <c r="K17" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="L17" s="1"/>
       <c r="M17">
         <v>5</v>
       </c>
@@ -4223,7 +4340,7 @@
         <v>5</v>
       </c>
       <c r="R17">
-        <f>SUM(M17:Q17)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
@@ -4258,6 +4375,7 @@
       <c r="K18" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="L18" s="1"/>
       <c r="M18">
         <v>2</v>
       </c>
@@ -4274,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <f>SUM(M18:Q18)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
@@ -4303,6 +4421,7 @@
       <c r="K19" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="L19" s="1"/>
       <c r="M19">
         <v>5</v>
       </c>
@@ -4319,7 +4438,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <f>SUM(M19:Q19)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="T19" s="1" t="s">
@@ -4348,6 +4467,7 @@
       <c r="J20" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="L20" s="1"/>
       <c r="M20">
         <v>5</v>
       </c>
@@ -4364,7 +4484,7 @@
         <v>5</v>
       </c>
       <c r="R20">
-        <f>SUM(M20:Q20)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -4393,6 +4513,7 @@
       <c r="K21" s="1" t="s">
         <v>88</v>
       </c>
+      <c r="L21" s="1"/>
       <c r="M21">
         <v>5</v>
       </c>
@@ -4409,7 +4530,7 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <f>SUM(M21:Q21)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -4444,6 +4565,7 @@
       <c r="K22" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="L22" s="1"/>
       <c r="M22">
         <v>1</v>
       </c>
@@ -4460,14 +4582,14 @@
         <v>1</v>
       </c>
       <c r="R22">
-        <f>SUM(M22:Q22)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>97</v>
       </c>
@@ -4495,7 +4617,7 @@
       <c r="K23" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" s="17" t="s">
         <v>644</v>
       </c>
       <c r="M23">
@@ -4514,14 +4636,14 @@
         <v>5</v>
       </c>
       <c r="R23">
-        <f>SUM(M23:Q23)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="S23" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>97</v>
       </c>
@@ -4549,7 +4671,7 @@
       <c r="K24" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="17" t="s">
         <v>645</v>
       </c>
       <c r="M24">
@@ -4568,7 +4690,7 @@
         <v>5</v>
       </c>
       <c r="R24">
-        <f>SUM(M24:Q24)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S24" t="s">
@@ -4578,7 +4700,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="110.4" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -4606,6 +4728,9 @@
       <c r="K25" s="1" t="s">
         <v>137</v>
       </c>
+      <c r="L25" s="17" t="s">
+        <v>652</v>
+      </c>
       <c r="M25">
         <v>5</v>
       </c>
@@ -4622,14 +4747,14 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <f>SUM(M25:Q25)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="S25" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -4657,6 +4782,9 @@
       <c r="K26" s="1" t="s">
         <v>131</v>
       </c>
+      <c r="L26" s="17" t="s">
+        <v>651</v>
+      </c>
       <c r="M26">
         <v>5</v>
       </c>
@@ -4673,7 +4801,7 @@
         <v>5</v>
       </c>
       <c r="R26">
-        <f>SUM(M26:Q26)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="S26" t="s">
@@ -4683,7 +4811,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>97</v>
       </c>
@@ -4711,6 +4839,9 @@
       <c r="K27" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="L27" s="17" t="s">
+        <v>650</v>
+      </c>
       <c r="M27">
         <v>3</v>
       </c>
@@ -4727,14 +4858,14 @@
         <v>2</v>
       </c>
       <c r="R27">
-        <f>SUM(M27:Q27)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S27" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>97</v>
       </c>
@@ -4762,6 +4893,9 @@
       <c r="K28" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="L28" s="17" t="s">
+        <v>647</v>
+      </c>
       <c r="M28">
         <v>5</v>
       </c>
@@ -4778,14 +4912,14 @@
         <v>5</v>
       </c>
       <c r="R28">
-        <f>SUM(M28:Q28)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S28" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>97</v>
       </c>
@@ -4813,6 +4947,9 @@
       <c r="K29" s="1" t="s">
         <v>114</v>
       </c>
+      <c r="L29" s="17" t="s">
+        <v>646</v>
+      </c>
       <c r="M29">
         <v>3</v>
       </c>
@@ -4829,14 +4966,14 @@
         <v>3</v>
       </c>
       <c r="R29">
-        <f>SUM(M29:Q29)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="S29" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4864,6 +5001,9 @@
       <c r="K30" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="L30" s="17" t="s">
+        <v>646</v>
+      </c>
       <c r="M30">
         <v>2</v>
       </c>
@@ -4880,14 +5020,14 @@
         <v>2</v>
       </c>
       <c r="R30">
-        <f>SUM(M30:Q30)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="S30" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="230.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="230.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -4915,7 +5055,7 @@
       <c r="K31" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="L31" s="17" t="s">
         <v>643</v>
       </c>
       <c r="M31">
@@ -4934,7 +5074,7 @@
         <v>2</v>
       </c>
       <c r="R31">
-        <f>SUM(M31:Q31)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S31" t="s">
@@ -4944,7 +5084,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -4972,6 +5112,9 @@
       <c r="K32" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="L32" s="17" t="s">
+        <v>649</v>
+      </c>
       <c r="M32">
         <v>3</v>
       </c>
@@ -4988,14 +5131,14 @@
         <v>1</v>
       </c>
       <c r="R32">
-        <f>SUM(M32:Q32)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="S32" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="129.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>97</v>
       </c>
@@ -5020,6 +5163,9 @@
       <c r="J33" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="L33" s="18" t="s">
+        <v>648</v>
+      </c>
       <c r="M33">
         <v>1</v>
       </c>
@@ -5036,14 +5182,14 @@
         <v>1</v>
       </c>
       <c r="R33">
-        <f>SUM(M33:Q33)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="S33" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -5071,6 +5217,9 @@
       <c r="K34" s="1" t="s">
         <v>198</v>
       </c>
+      <c r="L34" s="3" t="s">
+        <v>656</v>
+      </c>
       <c r="M34">
         <v>5</v>
       </c>
@@ -5087,14 +5236,14 @@
         <v>5</v>
       </c>
       <c r="R34">
-        <f>SUM(M34:Q34)</f>
+        <f t="shared" ref="R34:R65" si="1">SUM(M34:Q34)</f>
         <v>20</v>
       </c>
       <c r="S34" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -5122,6 +5271,9 @@
       <c r="K35" s="1" t="s">
         <v>237</v>
       </c>
+      <c r="L35" s="3" t="s">
+        <v>655</v>
+      </c>
       <c r="M35">
         <v>5</v>
       </c>
@@ -5138,14 +5290,14 @@
         <v>5</v>
       </c>
       <c r="R35">
-        <f>SUM(M35:Q35)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="S35" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>98</v>
       </c>
@@ -5173,6 +5325,9 @@
       <c r="K36" s="1" t="s">
         <v>214</v>
       </c>
+      <c r="L36" s="3" t="s">
+        <v>653</v>
+      </c>
       <c r="M36">
         <v>4</v>
       </c>
@@ -5189,14 +5344,14 @@
         <v>5</v>
       </c>
       <c r="R36">
-        <f>SUM(M36:Q36)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S36" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>98</v>
       </c>
@@ -5224,6 +5379,9 @@
       <c r="K37" s="1" t="s">
         <v>233</v>
       </c>
+      <c r="L37" s="3" t="s">
+        <v>654</v>
+      </c>
       <c r="M37">
         <v>4</v>
       </c>
@@ -5240,14 +5398,14 @@
         <v>5</v>
       </c>
       <c r="R37">
-        <f>SUM(M37:Q37)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S37" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="158.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>98</v>
       </c>
@@ -5275,6 +5433,9 @@
       <c r="K38" s="1" t="s">
         <v>304</v>
       </c>
+      <c r="L38" s="3" t="s">
+        <v>657</v>
+      </c>
       <c r="M38">
         <v>3</v>
       </c>
@@ -5291,7 +5452,7 @@
         <v>5</v>
       </c>
       <c r="R38">
-        <f>SUM(M38:Q38)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="S38" t="s">
@@ -5301,7 +5462,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>98</v>
       </c>
@@ -5329,6 +5490,9 @@
       <c r="K39" s="1" t="s">
         <v>205</v>
       </c>
+      <c r="L39" s="3" t="s">
+        <v>659</v>
+      </c>
       <c r="M39">
         <v>3</v>
       </c>
@@ -5345,7 +5509,7 @@
         <v>3</v>
       </c>
       <c r="R39">
-        <f>SUM(M39:Q39)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="S39" t="s">
@@ -5377,6 +5541,7 @@
       <c r="K40" s="1" t="s">
         <v>210</v>
       </c>
+      <c r="L40" s="1"/>
       <c r="M40">
         <v>4</v>
       </c>
@@ -5393,14 +5558,14 @@
         <v>5</v>
       </c>
       <c r="R40">
-        <f>SUM(M40:Q40)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="T40" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="144" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="144" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>98</v>
       </c>
@@ -5428,6 +5593,9 @@
       <c r="K41" s="1" t="s">
         <v>335</v>
       </c>
+      <c r="L41" s="3" t="s">
+        <v>660</v>
+      </c>
       <c r="M41">
         <v>4</v>
       </c>
@@ -5444,14 +5612,14 @@
         <v>5</v>
       </c>
       <c r="R41">
-        <f>SUM(M41:Q41)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="S41" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -5479,6 +5647,9 @@
       <c r="K42" s="1" t="s">
         <v>201</v>
       </c>
+      <c r="L42" s="3" t="s">
+        <v>661</v>
+      </c>
       <c r="M42">
         <v>5</v>
       </c>
@@ -5495,7 +5666,7 @@
         <v>5</v>
       </c>
       <c r="R42">
-        <f>SUM(M42:Q42)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S42" t="s">
@@ -5505,7 +5676,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="87" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="87" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -5533,6 +5704,9 @@
       <c r="K43" s="1" t="s">
         <v>207</v>
       </c>
+      <c r="L43" s="3" t="s">
+        <v>658</v>
+      </c>
       <c r="M43">
         <v>2</v>
       </c>
@@ -5549,7 +5723,7 @@
         <v>3</v>
       </c>
       <c r="R43">
-        <f>SUM(M43:Q43)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S43" t="s">
@@ -5559,7 +5733,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -5587,6 +5761,9 @@
       <c r="K44" s="1" t="s">
         <v>333</v>
       </c>
+      <c r="L44" s="3" t="s">
+        <v>664</v>
+      </c>
       <c r="M44">
         <v>4</v>
       </c>
@@ -5603,14 +5780,14 @@
         <v>1</v>
       </c>
       <c r="R44">
-        <f>SUM(M44:Q44)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S44" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -5638,6 +5815,9 @@
       <c r="K45" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="L45" s="3" t="s">
+        <v>663</v>
+      </c>
       <c r="M45">
         <v>4</v>
       </c>
@@ -5654,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="R45">
-        <f>SUM(M45:Q45)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="S45" t="s">
@@ -5664,7 +5844,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>338</v>
       </c>
@@ -5692,6 +5872,9 @@
       <c r="K46" s="1" t="s">
         <v>337</v>
       </c>
+      <c r="L46" s="3" t="s">
+        <v>662</v>
+      </c>
       <c r="M46">
         <v>2</v>
       </c>
@@ -5708,7 +5891,7 @@
         <v>5</v>
       </c>
       <c r="R46">
-        <f>SUM(M46:Q46)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="S46" t="s">
@@ -5737,6 +5920,7 @@
       <c r="J47" s="1" t="s">
         <v>194</v>
       </c>
+      <c r="L47" s="1"/>
       <c r="M47">
         <v>1</v>
       </c>
@@ -5753,7 +5937,7 @@
         <v>2</v>
       </c>
       <c r="R47">
-        <f>SUM(M47:Q47)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -5782,6 +5966,7 @@
       <c r="K48" s="1" t="s">
         <v>235</v>
       </c>
+      <c r="L48" s="1"/>
       <c r="M48">
         <v>3</v>
       </c>
@@ -5798,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="R48">
-        <f>SUM(M48:Q48)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -5827,6 +6012,7 @@
       <c r="K49" s="1" t="s">
         <v>250</v>
       </c>
+      <c r="L49" s="1"/>
       <c r="M49">
         <v>1</v>
       </c>
@@ -5843,7 +6029,7 @@
         <v>5</v>
       </c>
       <c r="R49">
-        <f>SUM(M49:Q49)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -5872,6 +6058,7 @@
       <c r="K50" s="1" t="s">
         <v>253</v>
       </c>
+      <c r="L50" s="1"/>
       <c r="M50">
         <v>1</v>
       </c>
@@ -5888,7 +6075,7 @@
         <v>5</v>
       </c>
       <c r="R50">
-        <f>SUM(M50:Q50)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -5917,6 +6104,7 @@
       <c r="K51" s="1" t="s">
         <v>275</v>
       </c>
+      <c r="L51" s="1"/>
       <c r="M51">
         <v>2</v>
       </c>
@@ -5933,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="R51">
-        <f>SUM(M51:Q51)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="T51" s="1" t="s">
@@ -5965,6 +6153,7 @@
       <c r="K52" s="1" t="s">
         <v>287</v>
       </c>
+      <c r="L52" s="1"/>
       <c r="M52">
         <v>1</v>
       </c>
@@ -5981,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="R52">
-        <f>SUM(M52:Q52)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -6010,6 +6199,7 @@
       <c r="K53" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="L53" s="1"/>
       <c r="M53">
         <v>3</v>
       </c>
@@ -6026,7 +6216,7 @@
         <v>1</v>
       </c>
       <c r="R53">
-        <f>SUM(M53:Q53)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -6052,6 +6242,7 @@
       <c r="J54" s="1" t="s">
         <v>255</v>
       </c>
+      <c r="L54" s="1"/>
       <c r="M54">
         <v>2</v>
       </c>
@@ -6068,7 +6259,7 @@
         <v>1</v>
       </c>
       <c r="R54">
-        <f>SUM(M54:Q54)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="T54" s="1" t="s">
@@ -6100,6 +6291,7 @@
       <c r="K55" s="1" t="s">
         <v>264</v>
       </c>
+      <c r="L55" s="1"/>
       <c r="M55">
         <v>2</v>
       </c>
@@ -6116,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="R55">
-        <f>SUM(M55:Q55)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -6145,6 +6337,7 @@
       <c r="K56" s="1" t="s">
         <v>265</v>
       </c>
+      <c r="L56" s="1"/>
       <c r="M56">
         <v>3</v>
       </c>
@@ -6161,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="R56">
-        <f>SUM(M56:Q56)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="T56" s="1" t="s">
@@ -6193,6 +6386,7 @@
       <c r="K57" s="1" t="s">
         <v>311</v>
       </c>
+      <c r="L57" s="1"/>
       <c r="M57">
         <v>4</v>
       </c>
@@ -6209,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="R57">
-        <f>SUM(M57:Q57)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="T57" s="1" t="s">
@@ -6241,6 +6435,7 @@
       <c r="K58" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="L58" s="1"/>
       <c r="M58">
         <v>2</v>
       </c>
@@ -6257,7 +6452,7 @@
         <v>1</v>
       </c>
       <c r="R58">
-        <f>SUM(M58:Q58)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -6283,6 +6478,7 @@
       <c r="J59" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="L59" s="1"/>
       <c r="M59">
         <v>3</v>
       </c>
@@ -6299,7 +6495,7 @@
         <v>1</v>
       </c>
       <c r="R59">
-        <f>SUM(M59:Q59)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="T59" s="1" t="s">
@@ -6331,6 +6527,7 @@
       <c r="K60" s="1" t="s">
         <v>259</v>
       </c>
+      <c r="L60" s="1"/>
       <c r="M60">
         <v>2</v>
       </c>
@@ -6347,7 +6544,7 @@
         <v>1</v>
       </c>
       <c r="R60">
-        <f>SUM(M60:Q60)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -6376,6 +6573,7 @@
       <c r="K61" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="L61" s="1"/>
       <c r="M61">
         <v>1</v>
       </c>
@@ -6392,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="R61">
-        <f>SUM(M61:Q61)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="T61" s="1" t="s">
@@ -6421,6 +6619,7 @@
       <c r="K62" s="1" t="s">
         <v>285</v>
       </c>
+      <c r="L62" s="1"/>
       <c r="M62">
         <v>1</v>
       </c>
@@ -6437,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="R62">
-        <f>SUM(M62:Q62)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -6466,6 +6665,7 @@
       <c r="K63" s="1" t="s">
         <v>302</v>
       </c>
+      <c r="L63" s="1"/>
       <c r="M63">
         <v>2</v>
       </c>
@@ -6482,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="R63">
-        <f>SUM(M63:Q63)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="T63" s="1" t="s">
@@ -6514,6 +6714,7 @@
       <c r="K64" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="L64" s="1"/>
       <c r="M64">
         <v>1</v>
       </c>
@@ -6530,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="R64">
-        <f>SUM(M64:Q64)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="T64" s="1" t="s">
@@ -6559,6 +6760,7 @@
       <c r="J65" s="1" t="s">
         <v>223</v>
       </c>
+      <c r="L65" s="1"/>
       <c r="M65">
         <v>3</v>
       </c>
@@ -6575,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="R65">
-        <f>SUM(M65:Q65)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -6604,6 +6806,7 @@
       <c r="K66" s="1" t="s">
         <v>228</v>
       </c>
+      <c r="L66" s="1"/>
       <c r="M66">
         <v>3</v>
       </c>
@@ -6620,7 +6823,7 @@
         <v>1</v>
       </c>
       <c r="R66">
-        <f>SUM(M66:Q66)</f>
+        <f t="shared" ref="R66:R97" si="2">SUM(M66:Q66)</f>
         <v>11</v>
       </c>
       <c r="T66" s="1" t="s">
@@ -6649,6 +6852,7 @@
       <c r="J67" s="1" t="s">
         <v>230</v>
       </c>
+      <c r="L67" s="1"/>
       <c r="M67">
         <v>2</v>
       </c>
@@ -6665,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="R67">
-        <f>SUM(M67:Q67)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T67" s="1" t="s">
@@ -6694,6 +6898,7 @@
       <c r="J68" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="L68" s="1"/>
       <c r="M68">
         <v>1</v>
       </c>
@@ -6710,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="R68">
-        <f>SUM(M68:Q68)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T68" s="1" t="s">
@@ -6742,6 +6947,7 @@
       <c r="K69" s="1" t="s">
         <v>249</v>
       </c>
+      <c r="L69" s="1"/>
       <c r="M69">
         <v>3</v>
       </c>
@@ -6758,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="R69">
-        <f>SUM(M69:Q69)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -6787,6 +6993,7 @@
       <c r="K70" s="1" t="s">
         <v>269</v>
       </c>
+      <c r="L70" s="1"/>
       <c r="M70">
         <v>1</v>
       </c>
@@ -6803,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="R70">
-        <f>SUM(M70:Q70)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -6832,6 +7039,7 @@
       <c r="K71" s="1" t="s">
         <v>295</v>
       </c>
+      <c r="L71" s="1"/>
       <c r="M71">
         <v>3</v>
       </c>
@@ -6848,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="R71">
-        <f>SUM(M71:Q71)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T71" s="1" t="s">
@@ -6880,6 +7088,7 @@
       <c r="K72" s="1" t="s">
         <v>298</v>
       </c>
+      <c r="L72" s="1"/>
       <c r="M72">
         <v>3</v>
       </c>
@@ -6896,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="R72">
-        <f>SUM(M72:Q72)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -6925,6 +7134,7 @@
       <c r="K73" s="1" t="s">
         <v>298</v>
       </c>
+      <c r="L73" s="1"/>
       <c r="M73">
         <v>3</v>
       </c>
@@ -6941,7 +7151,7 @@
         <v>1</v>
       </c>
       <c r="R73">
-        <f>SUM(M73:Q73)</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
     </row>
@@ -6970,6 +7180,7 @@
       <c r="K74" s="1" t="s">
         <v>197</v>
       </c>
+      <c r="L74" s="1"/>
       <c r="M74">
         <v>2</v>
       </c>
@@ -6986,7 +7197,7 @@
         <v>3</v>
       </c>
       <c r="R74">
-        <f>SUM(M74:Q74)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -7015,6 +7226,7 @@
       <c r="K75" s="1" t="s">
         <v>241</v>
       </c>
+      <c r="L75" s="1"/>
       <c r="M75">
         <v>2</v>
       </c>
@@ -7031,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="R75">
-        <f>SUM(M75:Q75)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -7060,6 +7272,7 @@
       <c r="K76" s="1" t="s">
         <v>246</v>
       </c>
+      <c r="L76" s="1"/>
       <c r="M76">
         <v>1</v>
       </c>
@@ -7076,7 +7289,7 @@
         <v>1</v>
       </c>
       <c r="R76">
-        <f>SUM(M76:Q76)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="T76" s="1" t="s">
@@ -7108,6 +7321,7 @@
       <c r="K77" s="1" t="s">
         <v>280</v>
       </c>
+      <c r="L77" s="1"/>
       <c r="M77">
         <v>2</v>
       </c>
@@ -7124,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="R77">
-        <f>SUM(M77:Q77)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -7153,6 +7367,7 @@
       <c r="K78" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="L78" s="1"/>
       <c r="M78">
         <v>2</v>
       </c>
@@ -7169,7 +7384,7 @@
         <v>1</v>
       </c>
       <c r="R78">
-        <f>SUM(M78:Q78)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -7198,6 +7413,7 @@
       <c r="K79" s="1" t="s">
         <v>308</v>
       </c>
+      <c r="L79" s="1"/>
       <c r="M79">
         <v>1</v>
       </c>
@@ -7214,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="R79">
-        <f>SUM(M79:Q79)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
@@ -7240,6 +7456,7 @@
       <c r="J80" s="1" t="s">
         <v>288</v>
       </c>
+      <c r="L80" s="1"/>
       <c r="M80">
         <v>1</v>
       </c>
@@ -7256,7 +7473,7 @@
         <v>1</v>
       </c>
       <c r="R80">
-        <f>SUM(M80:Q80)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -7277,8 +7494,9 @@
       <c r="J81" s="1" t="s">
         <v>312</v>
       </c>
+      <c r="L81" s="1"/>
       <c r="R81">
-        <f>SUM(M81:Q81)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S81" t="s">
@@ -7299,8 +7517,9 @@
         <v>1204</v>
       </c>
       <c r="I82"/>
+      <c r="L82" s="1"/>
       <c r="R82">
-        <f>SUM(M82:Q82)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S82" t="s">
@@ -7321,8 +7540,9 @@
         <v>18</v>
       </c>
       <c r="I83"/>
+      <c r="L83" s="1"/>
       <c r="R83">
-        <f>SUM(M83:Q83)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S83" t="s">
@@ -7343,8 +7563,9 @@
         <v>50</v>
       </c>
       <c r="I84"/>
+      <c r="L84" s="1"/>
       <c r="R84">
-        <f>SUM(M84:Q84)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S84" t="s">
@@ -7365,8 +7586,9 @@
         <v>453</v>
       </c>
       <c r="I85"/>
+      <c r="L85" s="1"/>
       <c r="R85">
-        <f>SUM(M85:Q85)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S85" t="s">
@@ -7387,8 +7609,9 @@
         <v>116</v>
       </c>
       <c r="I86"/>
+      <c r="L86" s="1"/>
       <c r="R86">
-        <f>SUM(M86:Q86)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S86" t="s">
@@ -7409,8 +7632,9 @@
         <v>23</v>
       </c>
       <c r="I87"/>
+      <c r="L87" s="1"/>
       <c r="R87">
-        <f>SUM(M87:Q87)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S87" t="s">
@@ -7431,8 +7655,9 @@
         <v>3289</v>
       </c>
       <c r="I88"/>
+      <c r="L88" s="1"/>
       <c r="R88">
-        <f>SUM(M88:Q88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S88" t="s">
@@ -7464,6 +7689,7 @@
       <c r="K89" s="1" t="s">
         <v>327</v>
       </c>
+      <c r="L89" s="1"/>
       <c r="M89">
         <v>4</v>
       </c>
@@ -7480,7 +7706,7 @@
         <v>5</v>
       </c>
       <c r="R89">
-        <f t="shared" ref="R87:R118" si="0">SUM(M89:Q89)</f>
+        <f t="shared" ref="R89:R93" si="3">SUM(M89:Q89)</f>
         <v>18</v>
       </c>
       <c r="T89" s="1" t="s">
@@ -7512,6 +7738,7 @@
       <c r="K90" s="1" t="s">
         <v>292</v>
       </c>
+      <c r="L90" s="1"/>
       <c r="M90">
         <v>1</v>
       </c>
@@ -7528,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="R90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T90" s="1" t="s">
@@ -7560,6 +7787,7 @@
       <c r="K91" s="1" t="s">
         <v>329</v>
       </c>
+      <c r="L91" s="1"/>
       <c r="M91">
         <v>1</v>
       </c>
@@ -7576,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="R91">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T91" s="1" t="s">
@@ -7605,6 +7833,7 @@
       <c r="J92" s="1" t="s">
         <v>283</v>
       </c>
+      <c r="L92" s="1"/>
       <c r="M92">
         <v>2</v>
       </c>
@@ -7621,7 +7850,7 @@
         <v>1</v>
       </c>
       <c r="R92">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T92" s="1" t="s">
@@ -7653,6 +7882,7 @@
       <c r="K93" s="1" t="s">
         <v>262</v>
       </c>
+      <c r="L93" s="1"/>
       <c r="M93">
         <v>1</v>
       </c>
@@ -7669,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="R93">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="T93" s="1" t="s">
@@ -7701,6 +7931,7 @@
       <c r="K94" s="1" t="s">
         <v>342</v>
       </c>
+      <c r="L94" s="1"/>
       <c r="M94">
         <v>2</v>
       </c>
@@ -7717,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="R94">
-        <f t="shared" ref="R94:R99" si="1">SUM(M94:Q94)</f>
+        <f t="shared" ref="R94:R99" si="4">SUM(M94:Q94)</f>
         <v>14</v>
       </c>
     </row>
@@ -7746,6 +7977,7 @@
       <c r="K95" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="L95" s="1"/>
       <c r="M95">
         <v>5</v>
       </c>
@@ -7762,7 +7994,7 @@
         <v>5</v>
       </c>
       <c r="R95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
     </row>
@@ -7791,6 +8023,7 @@
       <c r="K96" s="1" t="s">
         <v>347</v>
       </c>
+      <c r="L96" s="1"/>
       <c r="M96">
         <v>2</v>
       </c>
@@ -7807,7 +8040,7 @@
         <v>5</v>
       </c>
       <c r="R96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="T96" s="1" t="s">
@@ -7833,6 +8066,7 @@
       <c r="I97" s="1" t="s">
         <v>258</v>
       </c>
+      <c r="L97" s="1"/>
       <c r="M97">
         <v>2</v>
       </c>
@@ -7849,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="R97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
     </row>
@@ -7875,6 +8109,7 @@
       <c r="J98" s="1" t="s">
         <v>348</v>
       </c>
+      <c r="L98" s="1"/>
       <c r="M98">
         <v>3</v>
       </c>
@@ -7891,7 +8126,7 @@
         <v>5</v>
       </c>
       <c r="R98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -7917,6 +8152,7 @@
       <c r="J99" s="1" t="s">
         <v>350</v>
       </c>
+      <c r="L99" s="1"/>
       <c r="M99">
         <v>1</v>
       </c>
@@ -7933,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="R99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
     </row>
@@ -7941,7 +8177,7 @@
   <autoFilter ref="A1:T99" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="QA"/>
+        <filter val="TTI"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">

--- a/writings/Paper_Screening.xlsx
+++ b/writings/Paper_Screening.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMP9800\github\gradproj\writings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04D5781-1B5A-4FFB-AB0C-D4FCFA6C25F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381B5C66-63B5-4242-A19A-5B085D6C78F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="337" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="337" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2940,12 +2940,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -2986,7 +2992,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3039,8 +3045,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3615,7 +3627,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="144" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5163,7 +5175,7 @@
       <c r="J33" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L33" s="18" t="s">
+      <c r="L33" s="17" t="s">
         <v>648</v>
       </c>
       <c r="M33">
@@ -6823,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="R66">
-        <f t="shared" ref="R66:R97" si="2">SUM(M66:Q66)</f>
+        <f t="shared" ref="R66:R88" si="2">SUM(M66:Q66)</f>
         <v>11</v>
       </c>
       <c r="T66" s="1" t="s">
@@ -9105,7 +9117,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E22728-44DA-4F37-AFB8-E6A065276246}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK45"/>
   <sheetFormatPr defaultRowHeight="19.8" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9231,7 +9242,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="42.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>510</v>
       </c>
@@ -9460,7 +9471,7 @@
       </c>
     </row>
     <row r="4" spans="1:37" ht="43.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="20" t="s">
         <v>518</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -9801,7 +9812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>528</v>
       </c>
@@ -9915,7 +9926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="92.4" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="92.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>534</v>
       </c>
@@ -10029,7 +10040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>537</v>
       </c>
@@ -10143,7 +10154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>538</v>
       </c>
@@ -10255,7 +10266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>473</v>
       </c>
@@ -10369,7 +10380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>544</v>
       </c>
@@ -10483,7 +10494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="49.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>546</v>
       </c>
@@ -10595,7 +10606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>550</v>
       </c>
@@ -10709,7 +10720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>131</v>
       </c>
@@ -10821,7 +10832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>474</v>
       </c>
@@ -10935,7 +10946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="43.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>557</v>
       </c>
@@ -11049,7 +11060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="44.4" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>475</v>
       </c>
@@ -11277,7 +11288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="51.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>564</v>
       </c>
@@ -11391,7 +11402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="46.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>569</v>
       </c>
@@ -11505,7 +11516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="43.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>573</v>
       </c>
@@ -11619,7 +11630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="40.200000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>577</v>
       </c>
@@ -11733,7 +11744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>581</v>
       </c>
@@ -11847,7 +11858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="72" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="72" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>584</v>
       </c>
@@ -11961,7 +11972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>588</v>
       </c>
@@ -12075,7 +12086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>590</v>
       </c>
@@ -12189,7 +12200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>468</v>
       </c>
@@ -12303,7 +12314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>469</v>
       </c>
@@ -12417,7 +12428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>470</v>
       </c>
@@ -12529,7 +12540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>471</v>
       </c>
@@ -12641,7 +12652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>600</v>
       </c>
@@ -12753,7 +12764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="43.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>472</v>
       </c>
@@ -12866,7 +12877,7 @@
       </c>
     </row>
     <row r="34" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="18" t="s">
         <v>304</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -12977,7 +12988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>205</v>
       </c>
@@ -13088,7 +13099,7 @@
       </c>
     </row>
     <row r="36" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="19" t="s">
         <v>607</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -13201,7 +13212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="57.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>509</v>
       </c>
@@ -13313,7 +13324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>611</v>
       </c>
@@ -13427,7 +13438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>614</v>
       </c>
@@ -13541,7 +13552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>618</v>
       </c>
@@ -13655,7 +13666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>622</v>
       </c>
@@ -13769,7 +13780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>623</v>
       </c>
@@ -13883,7 +13894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="19.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" ht="19.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>625</v>
       </c>
@@ -13997,7 +14008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>632</v>
       </c>
@@ -14111,7 +14122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="28.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>634</v>
       </c>
@@ -14226,17 +14237,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK45" xr:uid="{F5E22728-44DA-4F37-AFB8-E6A065276246}">
-    <filterColumn colId="36">
-      <filters>
-        <filter val="10"/>
-        <filter val="2"/>
-        <filter val="3"/>
-        <filter val="4"/>
-        <filter val="9"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AK45" xr:uid="{F5E22728-44DA-4F37-AFB8-E6A065276246}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/writings/Paper_Screening.xlsx
+++ b/writings/Paper_Screening.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMP9800\github\gradproj\writings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381B5C66-63B5-4242-A19A-5B085D6C78F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7493439-1286-41C6-968F-47929715C811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="337" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="337" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="669">
   <si>
     <t>Title</t>
   </si>
@@ -2869,6 +2869,22 @@
   </si>
   <si>
     <t>Classification evaluation metrics for a variety of datasets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pogorelov, Konstantin, Kristin Ranheim Randel, Carsten Griwodz, et al. “KVASIR: A Multi-Class Image Dataset for Computer Aided Gastrointestinal Disease Detection.” Proceedings of the 8th ACM on Multimedia Systems Conference, ACM, June 20, 2017, 164–69. https://doi.org/10.1145/3083187.3083212.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kvasir Dataset</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Song, Yiming, Zhengjie Zhang, Ruilan Wang, et al. “CAS-Colon: A Comprehensive Colonoscopy Anatomical Segmentation Dataset for Artificial Intelligence Development.” Scientific Data 12 (August 2025): 1382. https://doi.org/10.1038/s41597-025-05588-3.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAS-COLON</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5201,7 +5217,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -5255,7 +5271,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>98</v>
       </c>
@@ -5309,7 +5325,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>98</v>
       </c>
@@ -5363,7 +5379,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>98</v>
       </c>
@@ -5417,7 +5433,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="158.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>98</v>
       </c>
@@ -5474,7 +5490,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>98</v>
       </c>
@@ -5577,7 +5593,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="144" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="144" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>98</v>
       </c>
@@ -5631,7 +5647,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>98</v>
       </c>
@@ -5688,7 +5704,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="87" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" ht="87" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>98</v>
       </c>
@@ -5745,7 +5761,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -5799,7 +5815,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>98</v>
       </c>
@@ -5856,7 +5872,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="100.8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="100.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>338</v>
       </c>
@@ -7489,7 +7505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>99</v>
       </c>
@@ -7515,7 +7531,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>99</v>
       </c>
@@ -7538,7 +7554,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="115.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>99</v>
       </c>
@@ -7561,7 +7577,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>99</v>
       </c>
@@ -7584,7 +7600,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="158.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -7607,7 +7623,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="86.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -7630,7 +7646,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="72" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="72" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -7653,7 +7669,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="72" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="72" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -8189,13 +8205,8 @@
   <autoFilter ref="A1:T99" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="TTI"/>
+        <filter val="Dataset"/>
       </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
     </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:T93">
@@ -8209,7 +8220,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84EF80BE-0DA4-44B6-8D40-C8D0EF1A7933}">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.77734375" style="1" customWidth="1"/>
@@ -9092,7 +9103,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -9100,12 +9111,34 @@
         <v>631</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="158.4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>633</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="129.6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="115.2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>668</v>
       </c>
     </row>
   </sheetData>
